--- a/Data/FlightPlan/FPL_22SEP26.xlsx
+++ b/Data/FlightPlan/FPL_22SEP26.xlsx
@@ -968,162 +968,165 @@
     <t>VN-A655</t>
   </si>
   <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>1382A *</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>VN-A674</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>ENH</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
     <t>06:05</t>
   </si>
   <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>VN-A685</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A687</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
     <t>08:15</t>
   </si>
   <si>
-    <t>1382A *</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>VN-A674</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>ENH</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>VN-A685</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A687</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
     <t>VN-A689</t>
   </si>
   <si>
@@ -1154,9 +1157,6 @@
     <t>VN-A699</t>
   </si>
   <si>
-    <t>05:20</t>
-  </si>
-  <si>
     <t>VN-A810</t>
   </si>
   <si>
@@ -1199,7 +1199,7 @@
     <t>Total Record(s): 364</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 21, 2026 20:55</t>
+    <t xml:space="preserve">Generated on  Sep 22, 2026 01:19</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3019,9 +3019,13 @@
       <c t="s" r="J49" s="7">
         <v>18</v>
       </c>
-      <c r="K49" s="7"/>
+      <c t="s" r="K49" s="7">
+        <v>97</v>
+      </c>
       <c r="L49" s="7"/>
-      <c r="M49" s="7"/>
+      <c t="s" r="M49" s="7">
+        <v>75</v>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c t="s" r="A50" s="6">
@@ -9711,7 +9715,7 @@
         <v>13</v>
       </c>
       <c r="B273" s="7">
-        <v>124</v>
+        <v>1372</v>
       </c>
       <c t="s" r="C273" s="7">
         <v>14</v>
@@ -9727,13 +9731,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>17</v>
+        <v>319</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>320</v>
+        <v>241</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9744,7 +9748,7 @@
         <v>13</v>
       </c>
       <c r="B274" s="7">
-        <v>129</v>
+        <v>1373</v>
       </c>
       <c t="s" r="C274" s="7">
         <v>14</v>
@@ -9757,16 +9761,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>17</v>
+        <v>319</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>182</v>
+        <v>227</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -10730,7 +10734,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c t="s" r="I306" s="7">
         <v>80</v>
@@ -10760,7 +10764,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>20</v>
@@ -10802,7 +10806,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -10835,7 +10839,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -10868,7 +10872,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -10901,7 +10905,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -10934,7 +10938,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -10982,7 +10986,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11015,7 +11019,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11048,7 +11052,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11081,7 +11085,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11129,7 +11133,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11162,7 +11166,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11195,7 +11199,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11228,7 +11232,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11276,7 +11280,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -11309,7 +11313,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
@@ -11324,7 +11328,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11342,7 +11346,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -11375,7 +11379,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -11408,7 +11412,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -11423,7 +11427,7 @@
         <v>247</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11456,7 +11460,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11468,7 +11472,7 @@
         <v>230</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>198</v>
@@ -11489,7 +11493,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11522,7 +11526,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11555,7 +11559,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11588,7 +11592,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11600,7 +11604,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>240</v>
@@ -11636,7 +11640,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -11669,7 +11673,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -11684,7 +11688,7 @@
         <v>173</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11702,7 +11706,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -11735,7 +11739,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -11750,7 +11754,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11768,7 +11772,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -11816,13 +11820,13 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
+        <v>347</v>
+      </c>
+      <c r="F343" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G343" s="8">
         <v>348</v>
-      </c>
-      <c r="F343" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G343" s="8">
-        <v>349</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>17</v>
@@ -11849,7 +11853,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -11882,7 +11886,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -11930,7 +11934,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -11963,7 +11967,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -11975,10 +11979,10 @@
         <v>294</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -11996,7 +12000,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12029,7 +12033,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12041,7 +12045,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>159</v>
@@ -12062,7 +12066,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12074,7 +12078,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>36</v>
@@ -12095,7 +12099,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12107,7 +12111,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>259</v>
@@ -12143,7 +12147,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12158,7 +12162,7 @@
         <v>309</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12176,7 +12180,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12209,7 +12213,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12218,7 +12222,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c t="s" r="I356" s="7">
         <v>157</v>
@@ -12242,13 +12246,13 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>17</v>
@@ -12275,7 +12279,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -12290,7 +12294,7 @@
         <v>327</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12323,7 +12327,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -12356,7 +12360,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
@@ -12389,7 +12393,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
@@ -12437,7 +12441,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12470,7 +12474,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12503,7 +12507,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12515,7 +12519,7 @@
         <v>267</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c t="s" r="J366" s="7">
         <v>87</v>
@@ -12536,7 +12540,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12569,7 +12573,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12584,7 +12588,7 @@
         <v>277</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12602,7 +12606,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12617,7 +12621,7 @@
         <v>145</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12650,7 +12654,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -12662,7 +12666,7 @@
         <v>161</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>319</v>
+        <v>363</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>56</v>
@@ -12683,7 +12687,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -12716,7 +12720,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -12728,7 +12732,7 @@
         <v>76</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c t="s" r="J373" s="7">
         <v>202</v>
@@ -12749,7 +12753,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -12782,7 +12786,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -12815,7 +12819,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -13091,7 +13095,7 @@
         <v>245</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13301,7 +13305,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>320</v>
+        <v>371</v>
       </c>
       <c t="s" r="J392" s="7">
         <v>74</v>
@@ -13469,7 +13473,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -13481,10 +13485,10 @@
         <v>304</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13502,7 +13506,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
@@ -13535,7 +13539,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
@@ -13568,7 +13572,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
@@ -13601,7 +13605,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F402" s="7">
         <v>320</v>
@@ -13610,13 +13614,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H402" s="8">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="I402" s="7">
         <v>191</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13634,13 +13638,13 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F403" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="H403" s="8">
         <v>20</v>
@@ -13682,7 +13686,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -13715,7 +13719,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -13741,14 +13745,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B407" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="C407" s="7">
         <v>14</v>
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -13785,7 +13789,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -13818,7 +13822,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -13866,7 +13870,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -13899,7 +13903,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -13908,7 +13912,7 @@
         <v>230</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="I412" s="7">
         <v>244</v>
@@ -13932,13 +13936,13 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G413" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="H413" s="8">
         <v>230</v>
@@ -13965,7 +13969,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -14013,7 +14017,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14046,7 +14050,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -14079,7 +14083,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14112,7 +14116,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -14145,7 +14149,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -14160,7 +14164,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14178,7 +14182,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -14219,14 +14223,14 @@
         <v>13</v>
       </c>
       <c r="B423" s="7">
-        <v>1372</v>
+        <v>124</v>
       </c>
       <c t="s" r="C423" s="7">
         <v>14</v>
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F423" s="7">
         <v>320</v>
@@ -14235,13 +14239,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H423" s="8">
-        <v>335</v>
+        <v>17</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>241</v>
+        <v>371</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14252,29 +14256,29 @@
         <v>13</v>
       </c>
       <c r="B424" s="7">
-        <v>1373</v>
+        <v>129</v>
       </c>
       <c t="s" r="C424" s="7">
         <v>14</v>
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F424" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G424" s="8">
-        <v>335</v>
+        <v>17</v>
       </c>
       <c t="s" r="H424" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>227</v>
+        <v>182</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -14292,7 +14296,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F425" s="7">
         <v>320</v>
@@ -14301,7 +14305,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c t="s" r="I425" s="7">
         <v>84</v>
@@ -14325,13 +14329,13 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>20</v>
@@ -14358,7 +14362,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F427" s="7">
         <v>320</v>
@@ -14391,7 +14395,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F428" s="7">
         <v>320</v>
@@ -14694,7 +14698,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>320</v>
+        <v>371</v>
       </c>
       <c t="s" r="J439" s="7">
         <v>130</v>
@@ -14933,7 +14937,7 @@
         <v>104</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>319</v>
+        <v>363</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>

--- a/Data/FlightPlan/FPL_22SEP26.xlsx
+++ b/Data/FlightPlan/FPL_22SEP26.xlsx
@@ -968,157 +968,178 @@
     <t>VN-A655</t>
   </si>
   <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>1382A *</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
     <t>VCL</t>
   </si>
   <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>08:02</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>VN-A674</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>ENH</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>VN-A685</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A687</t>
+  </si>
+  <si>
+    <t>431A *</t>
+  </si>
+  <si>
+    <t>VN-A689</t>
+  </si>
+  <si>
     <t>05:20</t>
   </si>
   <si>
-    <t>1382A *</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>VN-A674</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>ENH</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>VN-A685</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A687</t>
+    <t>CMB</t>
+  </si>
+  <si>
+    <t>VN-A693</t>
   </si>
   <si>
     <t>07:45</t>
@@ -1127,24 +1148,6 @@
     <t>08:15</t>
   </si>
   <si>
-    <t>VN-A689</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>CMB</t>
-  </si>
-  <si>
-    <t>VN-A693</t>
-  </si>
-  <si>
-    <t>431A *</t>
-  </si>
-  <si>
     <t>VN-A697</t>
   </si>
   <si>
@@ -1199,7 +1202,7 @@
     <t>Total Record(s): 364</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 22, 2026 01:19</t>
+    <t xml:space="preserve">Generated on  Sep 22, 2026 04:05</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -9715,7 +9718,7 @@
         <v>13</v>
       </c>
       <c r="B273" s="7">
-        <v>1372</v>
+        <v>801</v>
       </c>
       <c t="s" r="C273" s="7">
         <v>14</v>
@@ -9731,13 +9734,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H273" s="8">
+        <v>304</v>
+      </c>
+      <c t="s" r="I273" s="7">
         <v>319</v>
       </c>
-      <c t="s" r="I273" s="7">
+      <c t="s" r="J273" s="7">
         <v>320</v>
-      </c>
-      <c t="s" r="J273" s="7">
-        <v>241</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9748,7 +9751,7 @@
         <v>13</v>
       </c>
       <c r="B274" s="7">
-        <v>1373</v>
+        <v>802</v>
       </c>
       <c t="s" r="C274" s="7">
         <v>14</v>
@@ -9761,16 +9764,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>227</v>
+        <v>189</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>97</v>
+        <v>202</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -10734,7 +10737,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c t="s" r="I306" s="7">
         <v>80</v>
@@ -10764,7 +10767,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>20</v>
@@ -10806,7 +10809,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -10839,7 +10842,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -10872,7 +10875,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -10905,7 +10908,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -10938,7 +10941,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -10986,7 +10989,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11019,7 +11022,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11052,7 +11055,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11085,7 +11088,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11133,7 +11136,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11166,7 +11169,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11199,7 +11202,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11232,7 +11235,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11280,7 +11283,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -11313,7 +11316,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
@@ -11328,7 +11331,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11346,7 +11349,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -11379,7 +11382,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -11412,7 +11415,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -11427,7 +11430,7 @@
         <v>247</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11460,7 +11463,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11472,14 +11475,16 @@
         <v>230</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>198</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
-      <c r="M331" s="7"/>
+      <c t="s" r="M331" s="7">
+        <v>344</v>
+      </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
       <c t="s" r="A332" s="6">
@@ -11493,7 +11498,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11526,7 +11531,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11559,7 +11564,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11592,7 +11597,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11604,7 +11609,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>240</v>
@@ -11640,7 +11645,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -11673,7 +11678,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -11688,7 +11693,7 @@
         <v>173</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11706,7 +11711,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -11739,7 +11744,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -11754,7 +11759,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11772,7 +11777,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -11820,13 +11825,13 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>17</v>
@@ -11853,7 +11858,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -11886,7 +11891,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -11934,7 +11939,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -11967,7 +11972,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -11979,10 +11984,10 @@
         <v>294</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12000,7 +12005,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12033,7 +12038,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12045,7 +12050,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>159</v>
@@ -12066,7 +12071,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12078,7 +12083,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>36</v>
@@ -12099,7 +12104,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12111,7 +12116,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>259</v>
@@ -12147,7 +12152,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12162,7 +12167,7 @@
         <v>309</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12180,7 +12185,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12213,7 +12218,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12222,7 +12227,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c t="s" r="I356" s="7">
         <v>157</v>
@@ -12246,13 +12251,13 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>17</v>
@@ -12279,7 +12284,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -12294,7 +12299,7 @@
         <v>327</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12327,7 +12332,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -12360,7 +12365,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
@@ -12393,7 +12398,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
@@ -12441,7 +12446,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12474,7 +12479,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12507,7 +12512,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12519,7 +12524,7 @@
         <v>267</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="J366" s="7">
         <v>87</v>
@@ -12540,7 +12545,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12573,7 +12578,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12588,7 +12593,7 @@
         <v>277</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12606,7 +12611,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12621,7 +12626,7 @@
         <v>145</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12654,7 +12659,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -12666,7 +12671,7 @@
         <v>161</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>56</v>
@@ -12687,7 +12692,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -12699,7 +12704,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c t="s" r="J372" s="7">
         <v>243</v>
@@ -12720,7 +12725,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -12732,7 +12737,7 @@
         <v>76</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c t="s" r="J373" s="7">
         <v>202</v>
@@ -12753,7 +12758,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -12786,7 +12791,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -12819,7 +12824,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -12831,7 +12836,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>122</v>
@@ -12867,7 +12872,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -12900,7 +12905,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -12933,7 +12938,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -12966,7 +12971,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13014,7 +13019,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13047,7 +13052,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13080,7 +13085,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13095,7 +13100,7 @@
         <v>245</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13113,7 +13118,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13146,7 +13151,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13179,7 +13184,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -13212,7 +13217,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -13227,7 +13232,7 @@
         <v>253</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13253,14 +13258,14 @@
         <v>13</v>
       </c>
       <c r="B391" s="7">
-        <v>491</v>
+        <v>447</v>
       </c>
       <c t="s" r="C391" s="7">
         <v>14</v>
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13269,13 +13274,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>141</v>
+        <v>230</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>370</v>
+        <v>229</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13286,29 +13291,29 @@
         <v>13</v>
       </c>
       <c r="B392" s="7">
-        <v>492</v>
+        <v>440</v>
       </c>
       <c t="s" r="C392" s="7">
         <v>14</v>
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>141</v>
+        <v>230</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>371</v>
+        <v>75</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13318,15 +13323,15 @@
       <c t="s" r="A393" s="6">
         <v>13</v>
       </c>
-      <c r="B393" s="7">
-        <v>1491</v>
+      <c t="s" r="B393" s="7">
+        <v>372</v>
       </c>
       <c t="s" r="C393" s="7">
         <v>14</v>
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -13335,80 +13340,66 @@
         <v>17</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>311</v>
+        <v>218</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>107</v>
-      </c>
-      <c r="K393" s="7"/>
+        <v>66</v>
+      </c>
+      <c t="s" r="K393" s="7">
+        <v>218</v>
+      </c>
       <c r="L393" s="7"/>
-      <c r="M393" s="7"/>
+      <c t="s" r="M393" s="7">
+        <v>66</v>
+      </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
       <c t="s" r="A394" s="6">
         <v>13</v>
       </c>
       <c r="B394" s="7">
-        <v>1492</v>
+        <v>430</v>
       </c>
       <c t="s" r="C394" s="7">
         <v>14</v>
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>202</v>
+        <v>109</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>152</v>
+        <v>67</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c r="M394" s="7"/>
     </row>
     <row r="395" ht="15" customHeight="1">
-      <c t="s" r="A395" s="6">
-        <v>13</v>
-      </c>
-      <c r="B395" s="7">
-        <v>405</v>
-      </c>
-      <c t="s" r="C395" s="7">
-        <v>14</v>
-      </c>
+      <c r="A395" s="6"/>
+      <c r="B395" s="7"/>
+      <c r="C395" s="7"/>
       <c r="D395" s="7"/>
-      <c t="s" r="E395" s="7">
-        <v>369</v>
-      </c>
-      <c r="F395" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G395" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H395" s="8">
-        <v>45</v>
-      </c>
-      <c t="s" r="I395" s="7">
-        <v>87</v>
-      </c>
-      <c t="s" r="J395" s="7">
-        <v>233</v>
-      </c>
+      <c r="E395" s="7"/>
+      <c r="F395" s="7"/>
+      <c r="G395" s="8"/>
+      <c r="H395" s="8"/>
+      <c r="I395" s="7"/>
+      <c r="J395" s="7"/>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c r="M395" s="7"/>
@@ -13418,45 +13409,63 @@
         <v>13</v>
       </c>
       <c r="B396" s="7">
-        <v>406</v>
+        <v>1372</v>
       </c>
       <c t="s" r="C396" s="7">
         <v>14</v>
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F396" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>17</v>
+        <v>335</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>33</v>
+        <v>374</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>24</v>
+        <v>241</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c r="M396" s="7"/>
     </row>
     <row r="397" ht="14.25" customHeight="1">
-      <c r="A397" s="6"/>
-      <c r="B397" s="7"/>
-      <c r="C397" s="7"/>
+      <c t="s" r="A397" s="6">
+        <v>13</v>
+      </c>
+      <c r="B397" s="7">
+        <v>1373</v>
+      </c>
+      <c t="s" r="C397" s="7">
+        <v>14</v>
+      </c>
       <c r="D397" s="7"/>
-      <c r="E397" s="7"/>
-      <c r="F397" s="7"/>
-      <c r="G397" s="8"/>
-      <c r="H397" s="8"/>
-      <c r="I397" s="7"/>
-      <c r="J397" s="7"/>
+      <c t="s" r="E397" s="7">
+        <v>373</v>
+      </c>
+      <c r="F397" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G397" s="8">
+        <v>335</v>
+      </c>
+      <c t="s" r="H397" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="I397" s="7">
+        <v>227</v>
+      </c>
+      <c t="s" r="J397" s="7">
+        <v>97</v>
+      </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c r="M397" s="7"/>
@@ -13466,14 +13475,14 @@
         <v>13</v>
       </c>
       <c r="B398" s="7">
-        <v>801</v>
+        <v>382</v>
       </c>
       <c t="s" r="C398" s="7">
         <v>14</v>
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -13482,13 +13491,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>304</v>
+        <v>134</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>373</v>
+        <v>133</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>374</v>
+        <v>32</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13499,29 +13508,29 @@
         <v>13</v>
       </c>
       <c r="B399" s="7">
-        <v>802</v>
+        <v>383</v>
       </c>
       <c t="s" r="C399" s="7">
         <v>14</v>
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>304</v>
+        <v>134</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>189</v>
+        <v>66</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>202</v>
+        <v>110</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13532,14 +13541,14 @@
         <v>13</v>
       </c>
       <c r="B400" s="7">
-        <v>382</v>
+        <v>1875</v>
       </c>
       <c t="s" r="C400" s="7">
         <v>14</v>
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
@@ -13548,13 +13557,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>134</v>
+        <v>375</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>133</v>
+        <v>191</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>32</v>
+        <v>354</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13565,63 +13574,45 @@
         <v>13</v>
       </c>
       <c r="B401" s="7">
-        <v>383</v>
+        <v>1876</v>
       </c>
       <c t="s" r="C401" s="7">
         <v>14</v>
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>134</v>
+        <v>375</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>66</v>
+        <v>264</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c r="M401" s="7"/>
     </row>
     <row r="402" ht="14.25" customHeight="1">
-      <c t="s" r="A402" s="6">
-        <v>13</v>
-      </c>
-      <c r="B402" s="7">
-        <v>1875</v>
-      </c>
-      <c t="s" r="C402" s="7">
-        <v>14</v>
-      </c>
+      <c r="A402" s="6"/>
+      <c r="B402" s="7"/>
+      <c r="C402" s="7"/>
       <c r="D402" s="7"/>
-      <c t="s" r="E402" s="7">
-        <v>372</v>
-      </c>
-      <c r="F402" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G402" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="H402" s="8">
-        <v>375</v>
-      </c>
-      <c t="s" r="I402" s="7">
-        <v>191</v>
-      </c>
-      <c t="s" r="J402" s="7">
-        <v>352</v>
-      </c>
+      <c r="E402" s="7"/>
+      <c r="F402" s="7"/>
+      <c r="G402" s="8"/>
+      <c r="H402" s="8"/>
+      <c r="I402" s="7"/>
+      <c r="J402" s="7"/>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c r="M402" s="7"/>
@@ -13631,45 +13622,63 @@
         <v>13</v>
       </c>
       <c r="B403" s="7">
-        <v>1876</v>
+        <v>491</v>
       </c>
       <c t="s" r="C403" s="7">
         <v>14</v>
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F403" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>375</v>
+        <v>17</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>264</v>
+        <v>224</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>72</v>
+        <v>377</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c r="M403" s="7"/>
     </row>
     <row r="404" ht="14.25" customHeight="1">
-      <c r="A404" s="6"/>
-      <c r="B404" s="7"/>
-      <c r="C404" s="7"/>
+      <c t="s" r="A404" s="6">
+        <v>13</v>
+      </c>
+      <c r="B404" s="7">
+        <v>492</v>
+      </c>
+      <c t="s" r="C404" s="7">
+        <v>14</v>
+      </c>
       <c r="D404" s="7"/>
-      <c r="E404" s="7"/>
-      <c r="F404" s="7"/>
-      <c r="G404" s="8"/>
-      <c r="H404" s="8"/>
-      <c r="I404" s="7"/>
-      <c r="J404" s="7"/>
+      <c t="s" r="E404" s="7">
+        <v>376</v>
+      </c>
+      <c r="F404" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G404" s="8">
+        <v>141</v>
+      </c>
+      <c t="s" r="H404" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I404" s="7">
+        <v>378</v>
+      </c>
+      <c t="s" r="J404" s="7">
+        <v>74</v>
+      </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
       <c r="M404" s="7"/>
@@ -13679,7 +13688,7 @@
         <v>13</v>
       </c>
       <c r="B405" s="7">
-        <v>447</v>
+        <v>1491</v>
       </c>
       <c t="s" r="C405" s="7">
         <v>14</v>
@@ -13695,13 +13704,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>230</v>
+        <v>141</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>182</v>
+        <v>311</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>229</v>
+        <v>107</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13712,7 +13721,7 @@
         <v>13</v>
       </c>
       <c r="B406" s="7">
-        <v>440</v>
+        <v>1492</v>
       </c>
       <c t="s" r="C406" s="7">
         <v>14</v>
@@ -13725,16 +13734,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>230</v>
+        <v>141</v>
       </c>
       <c t="s" r="H406" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>75</v>
+        <v>202</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -13744,8 +13753,8 @@
       <c t="s" r="A407" s="6">
         <v>13</v>
       </c>
-      <c t="s" r="B407" s="7">
-        <v>377</v>
+      <c r="B407" s="7">
+        <v>405</v>
       </c>
       <c t="s" r="C407" s="7">
         <v>14</v>
@@ -13761,28 +13770,24 @@
         <v>17</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>134</v>
+        <v>45</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>218</v>
+        <v>87</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>66</v>
-      </c>
-      <c t="s" r="K407" s="7">
-        <v>218</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="K407" s="7"/>
       <c r="L407" s="7"/>
-      <c t="s" r="M407" s="7">
-        <v>66</v>
-      </c>
+      <c r="M407" s="7"/>
     </row>
     <row r="408" ht="14.25" customHeight="1">
       <c t="s" r="A408" s="6">
         <v>13</v>
       </c>
       <c r="B408" s="7">
-        <v>430</v>
+        <v>406</v>
       </c>
       <c t="s" r="C408" s="7">
         <v>14</v>
@@ -13795,16 +13800,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>134</v>
+        <v>45</v>
       </c>
       <c t="s" r="H408" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>109</v>
+        <v>33</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13870,7 +13875,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -13882,7 +13887,7 @@
         <v>230</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>275</v>
@@ -13903,7 +13908,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -13912,7 +13917,7 @@
         <v>230</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="I412" s="7">
         <v>244</v>
@@ -13936,13 +13941,13 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G413" s="8">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="H413" s="8">
         <v>230</v>
@@ -13969,7 +13974,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -14017,7 +14022,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14050,7 +14055,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -14083,7 +14088,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14116,7 +14121,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -14149,7 +14154,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -14164,7 +14169,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14182,7 +14187,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -14230,7 +14235,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F423" s="7">
         <v>320</v>
@@ -14242,10 +14247,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14263,7 +14268,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F424" s="7">
         <v>320</v>
@@ -14296,7 +14301,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F425" s="7">
         <v>320</v>
@@ -14305,7 +14310,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c t="s" r="I425" s="7">
         <v>84</v>
@@ -14329,13 +14334,13 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>20</v>
@@ -14362,7 +14367,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F427" s="7">
         <v>320</v>
@@ -14395,7 +14400,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F428" s="7">
         <v>320</v>
@@ -14443,7 +14448,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
@@ -14452,7 +14457,7 @@
         <v>119</v>
       </c>
       <c t="s" r="H430" s="8">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c t="s" r="I430" s="7">
         <v>118</v>
@@ -14476,13 +14481,13 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F431" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G431" s="8">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c t="s" r="H431" s="8">
         <v>119</v>
@@ -14524,13 +14529,13 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F433" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G433" s="8">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c t="s" r="H433" s="8">
         <v>119</v>
@@ -14557,7 +14562,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F434" s="7">
         <v>330</v>
@@ -14566,7 +14571,7 @@
         <v>119</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c t="s" r="I434" s="7">
         <v>113</v>
@@ -14605,7 +14610,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F436" s="7">
         <v>330</v>
@@ -14638,7 +14643,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F437" s="7">
         <v>330</v>
@@ -14647,7 +14652,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H437" s="8">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c t="s" r="I437" s="7">
         <v>95</v>
@@ -14686,7 +14691,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F439" s="7">
         <v>330</v>
@@ -14698,7 +14703,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c t="s" r="J439" s="7">
         <v>130</v>
@@ -14719,7 +14724,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F440" s="7">
         <v>330</v>
@@ -14767,7 +14772,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F442" s="7">
         <v>330</v>
@@ -14779,10 +14784,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
@@ -14800,7 +14805,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F443" s="7">
         <v>330</v>
@@ -14809,7 +14814,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H443" s="8">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c t="s" r="I443" s="7">
         <v>241</v>
@@ -14837,13 +14842,13 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F444" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G444" s="8">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c t="s" r="H444" s="8">
         <v>119</v>
@@ -14852,7 +14857,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c t="s" r="K444" s="7">
         <v>89</v>
@@ -14889,7 +14894,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F446" s="7">
         <v>330</v>
@@ -14898,7 +14903,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H446" s="8">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c t="s" r="I446" s="7">
         <v>275</v>
@@ -14922,13 +14927,13 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F447" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G447" s="8">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c t="s" r="H447" s="8">
         <v>20</v>
@@ -14937,7 +14942,7 @@
         <v>104</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
@@ -14945,7 +14950,7 @@
     </row>
     <row r="448" ht="15.75" customHeight="1">
       <c t="s" r="A448" s="9">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B448" s="9"/>
       <c r="C448" s="9"/>
@@ -14965,7 +14970,7 @@
     <row r="449" ht="65.25" customHeight="1"/>
     <row r="450" ht="17.25" customHeight="1">
       <c t="s" r="A450" s="10">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B450" s="10"/>
       <c r="C450" s="10"/>
@@ -14978,7 +14983,7 @@
       <c r="J450" s="10"/>
       <c r="K450" s="10"/>
       <c t="s" r="L450" s="11">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M450" s="11"/>
       <c r="N450" s="11"/>
